--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K289"/>
+  <dimension ref="A1:K299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -13510,16 +13510,16 @@
         <v>2026</v>
       </c>
       <c r="D257" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -13714,16 +13714,16 @@
         <v>2026</v>
       </c>
       <c r="D261" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -13736,12 +13736,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -13969,16 +13969,16 @@
         <v>2026</v>
       </c>
       <c r="D266" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Carine Georg</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>23774</t>
         </is>
       </c>
       <c r="H280" s="2" t="n">
@@ -14710,7 +14710,7 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Gabriel Coelho</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>23795</t>
         </is>
       </c>
       <c r="H281" s="2" t="n">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -14799,7 +14799,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>23433</t>
         </is>
       </c>
       <c r="H282" s="2" t="n">
@@ -14812,7 +14812,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -14836,21 +14836,21 @@
         <v>2026</v>
       </c>
       <c r="D283" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>23490</t>
         </is>
       </c>
       <c r="H283" s="2" t="n">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>23764</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="H284" s="2" t="n">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>23694</t>
         </is>
       </c>
       <c r="H285" s="2" t="n">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Carine Georg</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>23774</t>
+          <t>23764</t>
         </is>
       </c>
       <c r="H286" s="2" t="n">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -15033,7 +15033,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Gabriel Coelho</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>23795</t>
+          <t>23765</t>
         </is>
       </c>
       <c r="H287" s="2" t="n">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -15091,16 +15091,16 @@
         <v>2026</v>
       </c>
       <c r="D288" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -15142,21 +15142,21 @@
         <v>2026</v>
       </c>
       <c r="D289" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>23896</t>
         </is>
       </c>
       <c r="H289" s="2" t="n">
@@ -15164,7 +15164,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -15173,6 +15173,516 @@
         </is>
       </c>
       <c r="K289" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Elisandra Chaves</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D290" t="n">
+        <v>35</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>24062</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D291" t="n">
+        <v>35</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>24123</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Gabriel Coelho</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D292" t="n">
+        <v>35</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>24182</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Gabriel Coelho</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D293" t="n">
+        <v>35</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>24284</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D294" t="n">
+        <v>35</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>24307</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D295" t="n">
+        <v>35</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>24334</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D296" t="n">
+        <v>35</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>24412</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D297" t="n">
+        <v>35</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>24484</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D298" t="n">
+        <v>35</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>24488</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D299" t="n">
+        <v>35</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>24507</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -15189,7 +15699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K783"/>
+  <dimension ref="A1:K805"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49257,7 +49767,7 @@
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
@@ -49359,7 +49869,7 @@
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K670" t="inlineStr">
@@ -50532,7 +51042,7 @@
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
@@ -50736,7 +51246,7 @@
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
@@ -51042,7 +51552,7 @@
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
@@ -52776,7 +53286,7 @@
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K737" t="inlineStr">
@@ -52878,7 +53388,7 @@
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K739" t="inlineStr">
@@ -53252,7 +53762,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C747" t="n">
@@ -53286,7 +53796,7 @@
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
@@ -53337,7 +53847,7 @@
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
@@ -54221,7 +54731,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Nicolau Berlandi</t>
+          <t>Guilherme Worel</t>
         </is>
       </c>
       <c r="C766" t="n">
@@ -54255,7 +54765,7 @@
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K766" t="inlineStr">
@@ -54272,7 +54782,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Sostenes Silva</t>
+          <t>Cleovan Profeta</t>
         </is>
       </c>
       <c r="C767" t="n">
@@ -54293,11 +54803,11 @@
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>23674</t>
         </is>
       </c>
       <c r="H767" s="2" t="n">
-        <v>46113</v>
+        <v>46235</v>
       </c>
       <c r="I767" t="inlineStr">
         <is>
@@ -54306,7 +54816,7 @@
       </c>
       <c r="J767" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K767" t="inlineStr">
@@ -54323,28 +54833,28 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Gabriel López</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C768" t="n">
         <v>2026</v>
       </c>
       <c r="D768" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
         <is>
-          <t>23420</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="H768" s="2" t="n">
@@ -54352,7 +54862,7 @@
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
@@ -54395,7 +54905,7 @@
       </c>
       <c r="G769" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="H769" s="2" t="n">
@@ -54408,7 +54918,7 @@
       </c>
       <c r="J769" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K769" t="inlineStr">
@@ -54446,7 +54956,7 @@
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>23623</t>
         </is>
       </c>
       <c r="H770" s="2" t="n">
@@ -54459,7 +54969,7 @@
       </c>
       <c r="J770" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K770" t="inlineStr">
@@ -54476,7 +54986,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Maria Oliveira</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -54497,7 +55007,7 @@
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>23547</t>
+          <t>23679</t>
         </is>
       </c>
       <c r="H771" s="2" t="n">
@@ -54510,7 +55020,7 @@
       </c>
       <c r="J771" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K771" t="inlineStr">
@@ -54548,7 +55058,7 @@
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>23623</t>
+          <t>23689</t>
         </is>
       </c>
       <c r="H772" s="2" t="n">
@@ -54561,7 +55071,7 @@
       </c>
       <c r="J772" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K772" t="inlineStr">
@@ -54578,7 +55088,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C773" t="n">
@@ -54599,7 +55109,7 @@
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>23662</t>
+          <t>23737</t>
         </is>
       </c>
       <c r="H773" s="2" t="n">
@@ -54612,7 +55122,7 @@
       </c>
       <c r="J773" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K773" t="inlineStr">
@@ -54629,28 +55139,28 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Cleovan Profeta</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C774" t="n">
         <v>2026</v>
       </c>
       <c r="D774" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>23674</t>
+          <t>23747</t>
         </is>
       </c>
       <c r="H774" s="2" t="n">
@@ -54658,7 +55168,7 @@
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
@@ -54701,7 +55211,7 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>23679</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="H775" s="2" t="n">
@@ -54714,7 +55224,7 @@
       </c>
       <c r="J775" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K775" t="inlineStr">
@@ -54752,7 +55262,7 @@
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>23796</t>
         </is>
       </c>
       <c r="H776" s="2" t="n">
@@ -54765,7 +55275,7 @@
       </c>
       <c r="J776" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K776" t="inlineStr">
@@ -54782,7 +55292,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C777" t="n">
@@ -54803,7 +55313,7 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>23718</t>
+          <t>23821</t>
         </is>
       </c>
       <c r="H777" s="2" t="n">
@@ -54816,7 +55326,7 @@
       </c>
       <c r="J777" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K777" t="inlineStr">
@@ -54854,7 +55364,7 @@
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>23725</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="H778" s="2" t="n">
@@ -54867,7 +55377,7 @@
       </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K778" t="inlineStr">
@@ -54884,7 +55394,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C779" t="n">
@@ -54905,7 +55415,7 @@
       </c>
       <c r="G779" t="inlineStr">
         <is>
-          <t>23737</t>
+          <t>23547</t>
         </is>
       </c>
       <c r="H779" s="2" t="n">
@@ -54918,7 +55428,7 @@
       </c>
       <c r="J779" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K779" t="inlineStr">
@@ -54935,7 +55445,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -54956,7 +55466,7 @@
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="H780" s="2" t="n">
@@ -54969,7 +55479,7 @@
       </c>
       <c r="J780" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K780" t="inlineStr">
@@ -54986,7 +55496,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Sostenes Silva</t>
         </is>
       </c>
       <c r="C781" t="n">
@@ -55007,11 +55517,11 @@
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>23790</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="H781" s="2" t="n">
-        <v>46235</v>
+        <v>46113</v>
       </c>
       <c r="I781" t="inlineStr">
         <is>
@@ -55020,7 +55530,7 @@
       </c>
       <c r="J781" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K781" t="inlineStr">
@@ -55044,21 +55554,21 @@
         <v>2026</v>
       </c>
       <c r="D782" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>23796</t>
+          <t>23459</t>
         </is>
       </c>
       <c r="H782" s="2" t="n">
@@ -55066,7 +55576,7 @@
       </c>
       <c r="I782" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J782" t="inlineStr">
@@ -55095,21 +55605,21 @@
         <v>2026</v>
       </c>
       <c r="D783" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>23821</t>
+          <t>23825</t>
         </is>
       </c>
       <c r="H783" s="2" t="n">
@@ -55117,7 +55627,7 @@
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
@@ -55126,6 +55636,1128 @@
         </is>
       </c>
       <c r="K783" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D784" t="n">
+        <v>35</v>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>23942</t>
+        </is>
+      </c>
+      <c r="H784" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D785" t="n">
+        <v>35</v>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>24002</t>
+        </is>
+      </c>
+      <c r="H785" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D786" t="n">
+        <v>35</v>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>24087</t>
+        </is>
+      </c>
+      <c r="H786" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D787" t="n">
+        <v>35</v>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>24100</t>
+        </is>
+      </c>
+      <c r="H787" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D788" t="n">
+        <v>35</v>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>24204</t>
+        </is>
+      </c>
+      <c r="H788" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D789" t="n">
+        <v>35</v>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>24215</t>
+        </is>
+      </c>
+      <c r="H789" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D790" t="n">
+        <v>35</v>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>24222</t>
+        </is>
+      </c>
+      <c r="H790" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D791" t="n">
+        <v>35</v>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>24224</t>
+        </is>
+      </c>
+      <c r="H791" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D792" t="n">
+        <v>35</v>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>24226</t>
+        </is>
+      </c>
+      <c r="H792" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D793" t="n">
+        <v>35</v>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>24231</t>
+        </is>
+      </c>
+      <c r="H793" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D794" t="n">
+        <v>35</v>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>24245</t>
+        </is>
+      </c>
+      <c r="H794" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D795" t="n">
+        <v>35</v>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>24248</t>
+        </is>
+      </c>
+      <c r="H795" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D796" t="n">
+        <v>35</v>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>24287</t>
+        </is>
+      </c>
+      <c r="H796" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D797" t="n">
+        <v>35</v>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>24342</t>
+        </is>
+      </c>
+      <c r="H797" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D798" t="n">
+        <v>35</v>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>24343</t>
+        </is>
+      </c>
+      <c r="H798" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D799" t="n">
+        <v>35</v>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>24344</t>
+        </is>
+      </c>
+      <c r="H799" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D800" t="n">
+        <v>35</v>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>24366</t>
+        </is>
+      </c>
+      <c r="H800" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D801" t="n">
+        <v>35</v>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>24404</t>
+        </is>
+      </c>
+      <c r="H801" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D802" t="n">
+        <v>35</v>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>24416</t>
+        </is>
+      </c>
+      <c r="H802" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D803" t="n">
+        <v>35</v>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>24424</t>
+        </is>
+      </c>
+      <c r="H803" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D804" t="n">
+        <v>35</v>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>24444</t>
+        </is>
+      </c>
+      <c r="H804" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D805" t="n">
+        <v>35</v>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>24451</t>
+        </is>
+      </c>
+      <c r="H805" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K299"/>
+  <dimension ref="A1:K301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13510,16 +13510,16 @@
         <v>2026</v>
       </c>
       <c r="D257" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -13528,11 +13528,11 @@
         </is>
       </c>
       <c r="H257" s="2" t="n">
-        <v>46235</v>
+        <v>46245.70453703704</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -15118,7 +15118,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -15135,36 +15135,36 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Anderson Giese</t>
         </is>
       </c>
       <c r="C289" t="n">
         <v>2026</v>
       </c>
       <c r="D289" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>23896</t>
+          <t>24123</t>
         </is>
       </c>
       <c r="H289" s="2" t="n">
-        <v>46235</v>
+        <v>46265.58986111111</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -15237,36 +15237,36 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Anderson Giese</t>
+          <t>Gabriel Coelho</t>
         </is>
       </c>
       <c r="C291" t="n">
         <v>2026</v>
       </c>
       <c r="D291" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>24123</t>
+          <t>24182</t>
         </is>
       </c>
       <c r="H291" s="2" t="n">
-        <v>46235</v>
+        <v>46266.3849537037</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>24182</t>
+          <t>24284</t>
         </is>
       </c>
       <c r="H292" s="2" t="n">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Gabriel Coelho</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -15360,11 +15360,11 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>23896</t>
         </is>
       </c>
       <c r="H293" s="2" t="n">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -15397,16 +15397,16 @@
         <v>2026</v>
       </c>
       <c r="D294" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -15415,11 +15415,11 @@
         </is>
       </c>
       <c r="H294" s="2" t="n">
-        <v>46266</v>
+        <v>46267.6055324074</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -15441,36 +15441,36 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Mara Moraes</t>
+          <t>Higor Jesus</t>
         </is>
       </c>
       <c r="C295" t="n">
         <v>2026</v>
       </c>
       <c r="D295" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>24334</t>
+          <t>24412</t>
         </is>
       </c>
       <c r="H295" s="2" t="n">
-        <v>46266</v>
+        <v>46268.6827662037</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Higor Jesus</t>
+          <t>Mara Moraes</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>24412</t>
+          <t>24334</t>
         </is>
       </c>
       <c r="H296" s="2" t="n">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -15679,10 +15679,112 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Gabriel Coelho</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D300" t="n">
+        <v>36</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>24511</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="n">
+        <v>46273.29549768518</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr">
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D301" t="n">
+        <v>36</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>24693</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="n">
+        <v>46274.56839120371</v>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -15699,7 +15801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K805"/>
+  <dimension ref="A1:K836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51015,16 +51117,16 @@
         <v>2026</v>
       </c>
       <c r="D693" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
@@ -51033,16 +51135,16 @@
         </is>
       </c>
       <c r="H693" s="2" t="n">
-        <v>46235</v>
+        <v>46241.64128472222</v>
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
@@ -51525,16 +51627,16 @@
         <v>2026</v>
       </c>
       <c r="D703" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -51543,16 +51645,16 @@
         </is>
       </c>
       <c r="H703" s="2" t="n">
-        <v>46235</v>
+        <v>46241.55983796297</v>
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
@@ -51627,16 +51729,16 @@
         <v>2026</v>
       </c>
       <c r="D705" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -51645,16 +51747,16 @@
         </is>
       </c>
       <c r="H705" s="2" t="n">
-        <v>46235</v>
+        <v>46241.68315972222</v>
       </c>
       <c r="I705" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K705" t="inlineStr">
@@ -54867,7 +54969,7 @@
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K768" t="inlineStr">
@@ -55173,7 +55275,7 @@
       </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K774" t="inlineStr">
@@ -55581,7 +55683,7 @@
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K782" t="inlineStr">
@@ -55605,16 +55707,16 @@
         <v>2026</v>
       </c>
       <c r="D783" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
@@ -55623,11 +55725,11 @@
         </is>
       </c>
       <c r="H783" s="2" t="n">
-        <v>46235</v>
+        <v>46260.34043981481</v>
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
@@ -55683,7 +55785,7 @@
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K784" t="inlineStr">
@@ -55707,16 +55809,16 @@
         <v>2026</v>
       </c>
       <c r="D785" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
@@ -55725,11 +55827,11 @@
         </is>
       </c>
       <c r="H785" s="2" t="n">
-        <v>46235</v>
+        <v>46262.63327546296</v>
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
@@ -55758,16 +55860,16 @@
         <v>2026</v>
       </c>
       <c r="D786" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
@@ -55776,11 +55878,11 @@
         </is>
       </c>
       <c r="H786" s="2" t="n">
-        <v>46235</v>
+        <v>46265.43856481482</v>
       </c>
       <c r="I786" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J786" t="inlineStr">
@@ -55836,7 +55938,7 @@
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K787" t="inlineStr">
@@ -55887,7 +55989,7 @@
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K788" t="inlineStr">
@@ -55938,7 +56040,7 @@
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K789" t="inlineStr">
@@ -55989,7 +56091,7 @@
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K790" t="inlineStr">
@@ -56040,7 +56142,7 @@
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K791" t="inlineStr">
@@ -56091,7 +56193,7 @@
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K792" t="inlineStr">
@@ -56142,7 +56244,7 @@
       </c>
       <c r="J793" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K793" t="inlineStr">
@@ -56193,7 +56295,7 @@
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K794" t="inlineStr">
@@ -56244,7 +56346,7 @@
       </c>
       <c r="J795" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K795" t="inlineStr">
@@ -56295,7 +56397,7 @@
       </c>
       <c r="J796" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K796" t="inlineStr">
@@ -56346,7 +56448,7 @@
       </c>
       <c r="J797" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K797" t="inlineStr">
@@ -56397,7 +56499,7 @@
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K798" t="inlineStr">
@@ -56448,7 +56550,7 @@
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K799" t="inlineStr">
@@ -56499,7 +56601,7 @@
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K800" t="inlineStr">
@@ -56523,16 +56625,16 @@
         <v>2026</v>
       </c>
       <c r="D801" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="G801" t="inlineStr">
@@ -56541,11 +56643,11 @@
         </is>
       </c>
       <c r="H801" s="2" t="n">
-        <v>46266</v>
+        <v>46268.62138888889</v>
       </c>
       <c r="I801" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J801" t="inlineStr">
@@ -56601,7 +56703,7 @@
       </c>
       <c r="J802" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K802" t="inlineStr">
@@ -56652,7 +56754,7 @@
       </c>
       <c r="J803" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K803" t="inlineStr">
@@ -56676,16 +56778,16 @@
         <v>2026</v>
       </c>
       <c r="D804" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="G804" t="inlineStr">
@@ -56694,11 +56796,11 @@
         </is>
       </c>
       <c r="H804" s="2" t="n">
-        <v>46266</v>
+        <v>46269.43052083333</v>
       </c>
       <c r="I804" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J804" t="inlineStr">
@@ -56754,10 +56856,1591 @@
       </c>
       <c r="J805" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D806" t="n">
+        <v>36</v>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>24703</t>
+        </is>
+      </c>
+      <c r="H806" s="2" t="n">
+        <v>46274.62929398148</v>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K805" t="inlineStr">
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D807" t="n">
+        <v>36</v>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>24317</t>
+        </is>
+      </c>
+      <c r="H807" s="2" t="n">
+        <v>46267.63896990741</v>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D808" t="n">
+        <v>36</v>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>24376</t>
+        </is>
+      </c>
+      <c r="H808" s="2" t="n">
+        <v>46268.4737037037</v>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D809" t="n">
+        <v>36</v>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>24470</t>
+        </is>
+      </c>
+      <c r="H809" s="2" t="n">
+        <v>46269.63932870371</v>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D810" t="n">
+        <v>36</v>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>24571</t>
+        </is>
+      </c>
+      <c r="H810" s="2" t="n">
+        <v>46273.55194444444</v>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D811" t="n">
+        <v>36</v>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="H811" s="2" t="n">
+        <v>46273.69728009259</v>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D812" t="n">
+        <v>36</v>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>24687</t>
+        </is>
+      </c>
+      <c r="H812" s="2" t="n">
+        <v>46274.5191087963</v>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D813" t="n">
+        <v>36</v>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>24508</t>
+        </is>
+      </c>
+      <c r="H813" s="2" t="n">
+        <v>46272.69238425926</v>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D814" t="n">
+        <v>36</v>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>24579</t>
+        </is>
+      </c>
+      <c r="H814" s="2" t="n">
+        <v>46273.57678240741</v>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D815" t="n">
+        <v>36</v>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>24313</t>
+        </is>
+      </c>
+      <c r="H815" s="2" t="n">
+        <v>46267.63442129629</v>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D816" t="n">
+        <v>36</v>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>24314</t>
+        </is>
+      </c>
+      <c r="H816" s="2" t="n">
+        <v>46267.63511574074</v>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D817" t="n">
+        <v>36</v>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>24315</t>
+        </is>
+      </c>
+      <c r="H817" s="2" t="n">
+        <v>46267.63596064815</v>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D818" t="n">
+        <v>36</v>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>24316</t>
+        </is>
+      </c>
+      <c r="H818" s="2" t="n">
+        <v>46267.63686342593</v>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D819" t="n">
+        <v>36</v>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>24520</t>
+        </is>
+      </c>
+      <c r="H819" s="2" t="n">
+        <v>46273.33961805556</v>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D820" t="n">
+        <v>36</v>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>24582</t>
+        </is>
+      </c>
+      <c r="H820" s="2" t="n">
+        <v>46273.59018518519</v>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D821" t="n">
+        <v>36</v>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>24589</t>
+        </is>
+      </c>
+      <c r="H821" s="2" t="n">
+        <v>46273.60310185186</v>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D822" t="n">
+        <v>36</v>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>24591</t>
+        </is>
+      </c>
+      <c r="H822" s="2" t="n">
+        <v>46273.60751157408</v>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D823" t="n">
+        <v>36</v>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>24602</t>
+        </is>
+      </c>
+      <c r="H823" s="2" t="n">
+        <v>46273.64393518519</v>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D824" t="n">
+        <v>36</v>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>24615</t>
+        </is>
+      </c>
+      <c r="H824" s="2" t="n">
+        <v>46273.68373842593</v>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D825" t="n">
+        <v>36</v>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>24637</t>
+        </is>
+      </c>
+      <c r="H825" s="2" t="n">
+        <v>46274.28883101852</v>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D826" t="n">
+        <v>36</v>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>24639</t>
+        </is>
+      </c>
+      <c r="H826" s="2" t="n">
+        <v>46274.31292824074</v>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D827" t="n">
+        <v>36</v>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>24640</t>
+        </is>
+      </c>
+      <c r="H827" s="2" t="n">
+        <v>46274.31946759259</v>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D828" t="n">
+        <v>36</v>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>24652</t>
+        </is>
+      </c>
+      <c r="H828" s="2" t="n">
+        <v>46274.37930555556</v>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D829" t="n">
+        <v>36</v>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>24653</t>
+        </is>
+      </c>
+      <c r="H829" s="2" t="n">
+        <v>46274.37958333334</v>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D830" t="n">
+        <v>36</v>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>24657</t>
+        </is>
+      </c>
+      <c r="H830" s="2" t="n">
+        <v>46274.3891087963</v>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D831" t="n">
+        <v>36</v>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>24658</t>
+        </is>
+      </c>
+      <c r="H831" s="2" t="n">
+        <v>46274.38959490741</v>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D832" t="n">
+        <v>36</v>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>24669</t>
+        </is>
+      </c>
+      <c r="H832" s="2" t="n">
+        <v>46274.41993055555</v>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D833" t="n">
+        <v>36</v>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>24677</t>
+        </is>
+      </c>
+      <c r="H833" s="2" t="n">
+        <v>46274.45940972222</v>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Maria Oliveira</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D834" t="n">
+        <v>36</v>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>24526</t>
+        </is>
+      </c>
+      <c r="H834" s="2" t="n">
+        <v>46273.34725694444</v>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D835" t="n">
+        <v>36</v>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>21874</t>
+        </is>
+      </c>
+      <c r="H835" s="2" t="n">
+        <v>46230.41932870371</v>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D836" t="n">
+        <v>36</v>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>24465</t>
+        </is>
+      </c>
+      <c r="H836" s="2" t="n">
+        <v>46269.62844907407</v>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K301"/>
+  <dimension ref="A1:K305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -15142,16 +15142,16 @@
         <v>2026</v>
       </c>
       <c r="D289" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -15164,7 +15164,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -15781,10 +15781,214 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D302" t="n">
+        <v>37</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>24782</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="n">
+        <v>46275.61552083334</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Gabriel Coelho</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D303" t="n">
+        <v>37</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>24790</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="n">
+        <v>46275.64743055555</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D304" t="n">
+        <v>37</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>24936</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="n">
+        <v>46279.38700231481</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Elisandra Chaves</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D305" t="n">
+        <v>37</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>24982</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="n">
+        <v>46279.6369212963</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -15801,7 +16005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K836"/>
+  <dimension ref="A1:K848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51144,7 +51348,7 @@
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
@@ -51627,16 +51831,16 @@
         <v>2026</v>
       </c>
       <c r="D703" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -51649,7 +51853,7 @@
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
@@ -51756,7 +51960,7 @@
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K705" t="inlineStr">
@@ -55734,7 +55938,7 @@
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K783" t="inlineStr">
@@ -55836,7 +56040,7 @@
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K785" t="inlineStr">
@@ -55887,7 +56091,7 @@
       </c>
       <c r="J786" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K786" t="inlineStr">
@@ -56652,7 +56856,7 @@
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K801" t="inlineStr">
@@ -56805,7 +57009,7 @@
       </c>
       <c r="J804" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K804" t="inlineStr">
@@ -56907,7 +57111,7 @@
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K806" t="inlineStr">
@@ -56958,7 +57162,7 @@
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K807" t="inlineStr">
@@ -57009,7 +57213,7 @@
       </c>
       <c r="J808" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K808" t="inlineStr">
@@ -57033,16 +57237,16 @@
         <v>2026</v>
       </c>
       <c r="D809" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="G809" t="inlineStr">
@@ -57055,7 +57259,7 @@
       </c>
       <c r="I809" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="J809" t="inlineStr">
@@ -57084,16 +57288,16 @@
         <v>2026</v>
       </c>
       <c r="D810" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="G810" t="inlineStr">
@@ -57106,7 +57310,7 @@
       </c>
       <c r="I810" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="J810" t="inlineStr">
@@ -57162,7 +57366,7 @@
       </c>
       <c r="J811" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K811" t="inlineStr">
@@ -57213,7 +57417,7 @@
       </c>
       <c r="J812" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K812" t="inlineStr">
@@ -57264,7 +57468,7 @@
       </c>
       <c r="J813" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K813" t="inlineStr">
@@ -57281,7 +57485,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Maria Oliveira</t>
         </is>
       </c>
       <c r="C814" t="n">
@@ -57315,7 +57519,7 @@
       </c>
       <c r="J814" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K814" t="inlineStr">
@@ -57366,7 +57570,7 @@
       </c>
       <c r="J815" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K815" t="inlineStr">
@@ -57417,7 +57621,7 @@
       </c>
       <c r="J816" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K816" t="inlineStr">
@@ -57468,7 +57672,7 @@
       </c>
       <c r="J817" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K817" t="inlineStr">
@@ -57519,7 +57723,7 @@
       </c>
       <c r="J818" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K818" t="inlineStr">
@@ -57570,7 +57774,7 @@
       </c>
       <c r="J819" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K819" t="inlineStr">
@@ -57621,7 +57825,7 @@
       </c>
       <c r="J820" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K820" t="inlineStr">
@@ -57672,7 +57876,7 @@
       </c>
       <c r="J821" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K821" t="inlineStr">
@@ -57723,7 +57927,7 @@
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K822" t="inlineStr">
@@ -57774,7 +57978,7 @@
       </c>
       <c r="J823" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K823" t="inlineStr">
@@ -57825,7 +58029,7 @@
       </c>
       <c r="J824" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K824" t="inlineStr">
@@ -57876,7 +58080,7 @@
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K825" t="inlineStr">
@@ -57893,7 +58097,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Alana Oliveira</t>
         </is>
       </c>
       <c r="C826" t="n">
@@ -57927,7 +58131,7 @@
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K826" t="inlineStr">
@@ -57944,7 +58148,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Felipe Nascimento</t>
         </is>
       </c>
       <c r="C827" t="n">
@@ -57978,7 +58182,7 @@
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K827" t="inlineStr">
@@ -58029,7 +58233,7 @@
       </c>
       <c r="J828" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K828" t="inlineStr">
@@ -58080,7 +58284,7 @@
       </c>
       <c r="J829" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K829" t="inlineStr">
@@ -58131,7 +58335,7 @@
       </c>
       <c r="J830" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K830" t="inlineStr">
@@ -58182,7 +58386,7 @@
       </c>
       <c r="J831" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K831" t="inlineStr">
@@ -58233,7 +58437,7 @@
       </c>
       <c r="J832" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K832" t="inlineStr">
@@ -58284,7 +58488,7 @@
       </c>
       <c r="J833" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K833" t="inlineStr">
@@ -58335,7 +58539,7 @@
       </c>
       <c r="J834" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K834" t="inlineStr">
@@ -58386,7 +58590,7 @@
       </c>
       <c r="J835" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K835" t="inlineStr">
@@ -58437,10 +58641,622 @@
       </c>
       <c r="J836" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D837" t="n">
+        <v>37</v>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>24760</t>
+        </is>
+      </c>
+      <c r="H837" s="2" t="n">
+        <v>46275.48709490741</v>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K836" t="inlineStr">
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D838" t="n">
+        <v>37</v>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>24777</t>
+        </is>
+      </c>
+      <c r="H838" s="2" t="n">
+        <v>46275.5949537037</v>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D839" t="n">
+        <v>37</v>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>24909</t>
+        </is>
+      </c>
+      <c r="H839" s="2" t="n">
+        <v>46279.32311342593</v>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D840" t="n">
+        <v>37</v>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>24965</t>
+        </is>
+      </c>
+      <c r="H840" s="2" t="n">
+        <v>46279.55930555556</v>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D841" t="n">
+        <v>37</v>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="H841" s="2" t="n">
+        <v>46280.45483796296</v>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D842" t="n">
+        <v>37</v>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>25050</t>
+        </is>
+      </c>
+      <c r="H842" s="2" t="n">
+        <v>46280.51059027778</v>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D843" t="n">
+        <v>37</v>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>25058</t>
+        </is>
+      </c>
+      <c r="H843" s="2" t="n">
+        <v>46280.58413194444</v>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D844" t="n">
+        <v>37</v>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>25113</t>
+        </is>
+      </c>
+      <c r="H844" s="2" t="n">
+        <v>46281.36789351852</v>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D845" t="n">
+        <v>37</v>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>25198</t>
+        </is>
+      </c>
+      <c r="H845" s="2" t="n">
+        <v>46282.39790509259</v>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D846" t="n">
+        <v>37</v>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>24939</t>
+        </is>
+      </c>
+      <c r="H846" s="2" t="n">
+        <v>46279.39586805556</v>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D847" t="n">
+        <v>37</v>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>24809</t>
+        </is>
+      </c>
+      <c r="H847" s="2" t="n">
+        <v>46275.73388888889</v>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D848" t="n">
+        <v>37</v>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>25133</t>
+        </is>
+      </c>
+      <c r="H848" s="2" t="n">
+        <v>46281.46850694445</v>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K305"/>
+  <dimension ref="A1:K309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15169,7 +15169,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -15805,16 +15805,16 @@
         <v>2026</v>
       </c>
       <c r="D302" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -15985,10 +15985,222 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D306" t="n">
+        <v>38</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>25423</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:03:52</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D307" t="n">
+        <v>38</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>25463</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>2026-09-21 17:09:24</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Gabriel Coelho</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D308" t="n">
+        <v>38</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>25432</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:47:27</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D309" t="n">
+        <v>38</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>25528</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:22:42</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -16005,7 +16217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K848"/>
+  <dimension ref="A1:K861"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51831,16 +52043,16 @@
         <v>2026</v>
       </c>
       <c r="D703" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -51853,7 +52065,7 @@
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
@@ -57264,7 +57476,7 @@
       </c>
       <c r="J809" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K809" t="inlineStr">
@@ -57315,7 +57527,7 @@
       </c>
       <c r="J810" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K810" t="inlineStr">
@@ -58665,16 +58877,16 @@
         <v>2026</v>
       </c>
       <c r="D837" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="G837" t="inlineStr">
@@ -58687,7 +58899,7 @@
       </c>
       <c r="I837" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J837" t="inlineStr">
@@ -58743,7 +58955,7 @@
       </c>
       <c r="J838" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K838" t="inlineStr">
@@ -58767,16 +58979,16 @@
         <v>2026</v>
       </c>
       <c r="D839" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="G839" t="inlineStr">
@@ -58789,7 +59001,7 @@
       </c>
       <c r="I839" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J839" t="inlineStr">
@@ -58818,16 +59030,16 @@
         <v>2026</v>
       </c>
       <c r="D840" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="G840" t="inlineStr">
@@ -58840,7 +59052,7 @@
       </c>
       <c r="I840" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J840" t="inlineStr">
@@ -58896,7 +59108,7 @@
       </c>
       <c r="J841" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K841" t="inlineStr">
@@ -58920,16 +59132,16 @@
         <v>2026</v>
       </c>
       <c r="D842" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="G842" t="inlineStr">
@@ -58942,7 +59154,7 @@
       </c>
       <c r="I842" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J842" t="inlineStr">
@@ -58971,16 +59183,16 @@
         <v>2026</v>
       </c>
       <c r="D843" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="G843" t="inlineStr">
@@ -58993,7 +59205,7 @@
       </c>
       <c r="I843" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J843" t="inlineStr">
@@ -59022,16 +59234,16 @@
         <v>2026</v>
       </c>
       <c r="D844" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="G844" t="inlineStr">
@@ -59044,7 +59256,7 @@
       </c>
       <c r="I844" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J844" t="inlineStr">
@@ -59100,7 +59312,7 @@
       </c>
       <c r="J845" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K845" t="inlineStr">
@@ -59124,16 +59336,16 @@
         <v>2026</v>
       </c>
       <c r="D846" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="G846" t="inlineStr">
@@ -59146,7 +59358,7 @@
       </c>
       <c r="I846" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J846" t="inlineStr">
@@ -59175,16 +59387,16 @@
         <v>2026</v>
       </c>
       <c r="D847" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="G847" t="inlineStr">
@@ -59197,7 +59409,7 @@
       </c>
       <c r="I847" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="J847" t="inlineStr">
@@ -59253,10 +59465,699 @@
       </c>
       <c r="J848" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D849" t="n">
+        <v>38</v>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>25575</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>2026-09-23 06:01:04</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K848" t="inlineStr">
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D850" t="n">
+        <v>38</v>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>25576</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>2026-09-23 06:01:10</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D851" t="n">
+        <v>38</v>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>25577</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>2026-09-23 06:02:02</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C852" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D852" t="n">
+        <v>38</v>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>25325</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:25:02</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C853" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D853" t="n">
+        <v>38</v>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>25517</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>2026-09-22 10:42:03</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C854" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D854" t="n">
+        <v>38</v>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>25523</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:10:25</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C855" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D855" t="n">
+        <v>38</v>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>25543</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:46:43</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C856" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D856" t="n">
+        <v>38</v>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>25622</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:58:56</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Gabriel López</t>
+        </is>
+      </c>
+      <c r="C857" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D857" t="n">
+        <v>38</v>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>25642</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:41:55</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C858" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D858" t="n">
+        <v>38</v>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>25536</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:14:22</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C859" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D859" t="n">
+        <v>38</v>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>25561</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:02:41</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C860" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D860" t="n">
+        <v>38</v>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>25521</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:05:07</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C861" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D861" t="n">
+        <v>38</v>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>25621</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:52:06</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K861" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="H302" s="2" t="n">
-        <v>46275.61552083334</v>
+        <v>46275.64743055555</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
@@ -16026,10 +16026,8 @@
           <t>25423</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:03:52</t>
-        </is>
+      <c r="H306" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -16079,10 +16077,8 @@
           <t>25463</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>2026-09-21 17:09:24</t>
-        </is>
+      <c r="H307" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
@@ -16132,10 +16128,8 @@
           <t>25432</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>2026-09-21 13:47:27</t>
-        </is>
+      <c r="H308" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
@@ -16185,10 +16179,8 @@
           <t>25528</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>2026-09-22 13:22:42</t>
-        </is>
+      <c r="H309" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
@@ -52061,7 +52053,7 @@
         </is>
       </c>
       <c r="H703" s="2" t="n">
-        <v>46241.55983796297</v>
+        <v>46265.58986111111</v>
       </c>
       <c r="I703" t="inlineStr">
         <is>
@@ -58895,7 +58887,7 @@
         </is>
       </c>
       <c r="H837" s="2" t="n">
-        <v>46275.48709490741</v>
+        <v>46275.64743055555</v>
       </c>
       <c r="I837" t="inlineStr">
         <is>
@@ -58997,7 +58989,7 @@
         </is>
       </c>
       <c r="H839" s="2" t="n">
-        <v>46279.32311342593</v>
+        <v>46275.64743055555</v>
       </c>
       <c r="I839" t="inlineStr">
         <is>
@@ -59048,7 +59040,7 @@
         </is>
       </c>
       <c r="H840" s="2" t="n">
-        <v>46279.55930555556</v>
+        <v>46275.64743055555</v>
       </c>
       <c r="I840" t="inlineStr">
         <is>
@@ -59150,7 +59142,7 @@
         </is>
       </c>
       <c r="H842" s="2" t="n">
-        <v>46280.51059027778</v>
+        <v>46275.64743055555</v>
       </c>
       <c r="I842" t="inlineStr">
         <is>
@@ -59201,7 +59193,7 @@
         </is>
       </c>
       <c r="H843" s="2" t="n">
-        <v>46280.58413194444</v>
+        <v>46275.64743055555</v>
       </c>
       <c r="I843" t="inlineStr">
         <is>
@@ -59252,7 +59244,7 @@
         </is>
       </c>
       <c r="H844" s="2" t="n">
-        <v>46281.36789351852</v>
+        <v>46275.64743055555</v>
       </c>
       <c r="I844" t="inlineStr">
         <is>
@@ -59354,7 +59346,7 @@
         </is>
       </c>
       <c r="H846" s="2" t="n">
-        <v>46279.39586805556</v>
+        <v>46275.64743055555</v>
       </c>
       <c r="I846" t="inlineStr">
         <is>
@@ -59405,7 +59397,7 @@
         </is>
       </c>
       <c r="H847" s="2" t="n">
-        <v>46275.73388888889</v>
+        <v>46275.64743055555</v>
       </c>
       <c r="I847" t="inlineStr">
         <is>
@@ -59506,10 +59498,8 @@
           <t>25575</t>
         </is>
       </c>
-      <c r="H849" t="inlineStr">
-        <is>
-          <t>2026-09-23 06:01:04</t>
-        </is>
+      <c r="H849" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I849" t="inlineStr">
         <is>
@@ -59559,10 +59549,8 @@
           <t>25576</t>
         </is>
       </c>
-      <c r="H850" t="inlineStr">
-        <is>
-          <t>2026-09-23 06:01:10</t>
-        </is>
+      <c r="H850" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I850" t="inlineStr">
         <is>
@@ -59612,10 +59600,8 @@
           <t>25577</t>
         </is>
       </c>
-      <c r="H851" t="inlineStr">
-        <is>
-          <t>2026-09-23 06:02:02</t>
-        </is>
+      <c r="H851" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I851" t="inlineStr">
         <is>
@@ -59665,10 +59651,8 @@
           <t>25325</t>
         </is>
       </c>
-      <c r="H852" t="inlineStr">
-        <is>
-          <t>2026-09-18 15:25:02</t>
-        </is>
+      <c r="H852" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I852" t="inlineStr">
         <is>
@@ -59718,10 +59702,8 @@
           <t>25517</t>
         </is>
       </c>
-      <c r="H853" t="inlineStr">
-        <is>
-          <t>2026-09-22 10:42:03</t>
-        </is>
+      <c r="H853" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I853" t="inlineStr">
         <is>
@@ -59771,10 +59753,8 @@
           <t>25523</t>
         </is>
       </c>
-      <c r="H854" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:10:25</t>
-        </is>
+      <c r="H854" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I854" t="inlineStr">
         <is>
@@ -59824,10 +59804,8 @@
           <t>25543</t>
         </is>
       </c>
-      <c r="H855" t="inlineStr">
-        <is>
-          <t>2026-09-22 14:46:43</t>
-        </is>
+      <c r="H855" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -59877,10 +59855,8 @@
           <t>25622</t>
         </is>
       </c>
-      <c r="H856" t="inlineStr">
-        <is>
-          <t>2026-09-23 10:58:56</t>
-        </is>
+      <c r="H856" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I856" t="inlineStr">
         <is>
@@ -59930,10 +59906,8 @@
           <t>25642</t>
         </is>
       </c>
-      <c r="H857" t="inlineStr">
-        <is>
-          <t>2026-09-23 14:41:55</t>
-        </is>
+      <c r="H857" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I857" t="inlineStr">
         <is>
@@ -59983,10 +59957,8 @@
           <t>25536</t>
         </is>
       </c>
-      <c r="H858" t="inlineStr">
-        <is>
-          <t>2026-09-22 14:14:22</t>
-        </is>
+      <c r="H858" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I858" t="inlineStr">
         <is>
@@ -60036,10 +60008,8 @@
           <t>25561</t>
         </is>
       </c>
-      <c r="H859" t="inlineStr">
-        <is>
-          <t>2026-09-22 17:02:41</t>
-        </is>
+      <c r="H859" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I859" t="inlineStr">
         <is>
@@ -60089,10 +60059,8 @@
           <t>25521</t>
         </is>
       </c>
-      <c r="H860" t="inlineStr">
-        <is>
-          <t>2026-09-22 11:05:07</t>
-        </is>
+      <c r="H860" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I860" t="inlineStr">
         <is>
@@ -60142,10 +60110,8 @@
           <t>25621</t>
         </is>
       </c>
-      <c r="H861" t="inlineStr">
-        <is>
-          <t>2026-09-23 10:52:06</t>
-        </is>
+      <c r="H861" s="2" t="n">
+        <v>46275.64743055555</v>
       </c>
       <c r="I861" t="inlineStr">
         <is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K309"/>
+  <dimension ref="A1:K312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -16060,16 +16060,16 @@
         <v>2026</v>
       </c>
       <c r="D307" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -16078,11 +16078,11 @@
         </is>
       </c>
       <c r="H307" s="2" t="n">
-        <v>46275.64743055555</v>
+        <v>46286.71486111111</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -16162,16 +16162,16 @@
         <v>2026</v>
       </c>
       <c r="D309" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -16180,11 +16180,11 @@
         </is>
       </c>
       <c r="H309" s="2" t="n">
-        <v>46275.64743055555</v>
+        <v>46287.55743055556</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -16193,6 +16193,159 @@
         </is>
       </c>
       <c r="K309" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D310" t="n">
+        <v>39</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>25951</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="n">
+        <v>46293.66871527778</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D311" t="n">
+        <v>39</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>25985</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="n">
+        <v>46294.3765162037</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Gabriel Coelho</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D312" t="n">
+        <v>39</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>26080</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="n">
+        <v>46295.46240740741</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -16209,7 +16362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K861"/>
+  <dimension ref="A1:K876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52035,16 +52188,16 @@
         <v>2026</v>
       </c>
       <c r="D703" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -52053,11 +52206,11 @@
         </is>
       </c>
       <c r="H703" s="2" t="n">
-        <v>46265.58986111111</v>
+        <v>46241.55983796297</v>
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
@@ -58896,7 +59049,7 @@
       </c>
       <c r="J837" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K837" t="inlineStr">
@@ -58998,7 +59151,7 @@
       </c>
       <c r="J839" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K839" t="inlineStr">
@@ -59049,7 +59202,7 @@
       </c>
       <c r="J840" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K840" t="inlineStr">
@@ -59151,7 +59304,7 @@
       </c>
       <c r="J842" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K842" t="inlineStr">
@@ -59202,7 +59355,7 @@
       </c>
       <c r="J843" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K843" t="inlineStr">
@@ -59253,7 +59406,7 @@
       </c>
       <c r="J844" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K844" t="inlineStr">
@@ -59328,16 +59481,16 @@
         <v>2026</v>
       </c>
       <c r="D846" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="G846" t="inlineStr">
@@ -59346,11 +59499,11 @@
         </is>
       </c>
       <c r="H846" s="2" t="n">
-        <v>46275.64743055555</v>
+        <v>46279.39586805556</v>
       </c>
       <c r="I846" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="J846" t="inlineStr">
@@ -59379,16 +59532,16 @@
         <v>2026</v>
       </c>
       <c r="D847" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="G847" t="inlineStr">
@@ -59397,11 +59550,11 @@
         </is>
       </c>
       <c r="H847" s="2" t="n">
-        <v>46275.64743055555</v>
+        <v>46275.73388888889</v>
       </c>
       <c r="I847" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="J847" t="inlineStr">
@@ -59508,7 +59661,7 @@
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K849" t="inlineStr">
@@ -59559,7 +59712,7 @@
       </c>
       <c r="J850" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K850" t="inlineStr">
@@ -59610,7 +59763,7 @@
       </c>
       <c r="J851" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K851" t="inlineStr">
@@ -59661,7 +59814,7 @@
       </c>
       <c r="J852" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K852" t="inlineStr">
@@ -59712,7 +59865,7 @@
       </c>
       <c r="J853" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K853" t="inlineStr">
@@ -59763,7 +59916,7 @@
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K854" t="inlineStr">
@@ -59814,7 +59967,7 @@
       </c>
       <c r="J855" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K855" t="inlineStr">
@@ -59865,7 +60018,7 @@
       </c>
       <c r="J856" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K856" t="inlineStr">
@@ -59916,7 +60069,7 @@
       </c>
       <c r="J857" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K857" t="inlineStr">
@@ -59967,7 +60120,7 @@
       </c>
       <c r="J858" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K858" t="inlineStr">
@@ -59991,16 +60144,16 @@
         <v>2026</v>
       </c>
       <c r="D859" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="G859" t="inlineStr">
@@ -60009,11 +60162,11 @@
         </is>
       </c>
       <c r="H859" s="2" t="n">
-        <v>46275.64743055555</v>
+        <v>46287.71019675926</v>
       </c>
       <c r="I859" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="J859" t="inlineStr">
@@ -60069,7 +60222,7 @@
       </c>
       <c r="J860" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K860" t="inlineStr">
@@ -60120,10 +60273,775 @@
       </c>
       <c r="J861" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C862" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D862" t="n">
+        <v>39</v>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>25406</t>
+        </is>
+      </c>
+      <c r="H862" s="2" t="n">
+        <v>46286.40253472222</v>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K861" t="inlineStr">
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C863" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D863" t="n">
+        <v>39</v>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>25719</t>
+        </is>
+      </c>
+      <c r="H863" s="2" t="n">
+        <v>46289.57453703704</v>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C864" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D864" t="n">
+        <v>39</v>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>25793</t>
+        </is>
+      </c>
+      <c r="H864" s="2" t="n">
+        <v>46290.41263888889</v>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C865" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D865" t="n">
+        <v>39</v>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>25818</t>
+        </is>
+      </c>
+      <c r="H865" s="2" t="n">
+        <v>46290.62369212963</v>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Cleovan Profeta</t>
+        </is>
+      </c>
+      <c r="C866" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D866" t="n">
+        <v>39</v>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>25827</t>
+        </is>
+      </c>
+      <c r="H866" s="2" t="n">
+        <v>46290.64403935185</v>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>patrick doyle</t>
+        </is>
+      </c>
+      <c r="C867" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D867" t="n">
+        <v>39</v>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>25869</t>
+        </is>
+      </c>
+      <c r="H867" s="2" t="n">
+        <v>46293.30106481481</v>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C868" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D868" t="n">
+        <v>39</v>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>25887</t>
+        </is>
+      </c>
+      <c r="H868" s="2" t="n">
+        <v>46293.37362268518</v>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C869" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D869" t="n">
+        <v>39</v>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>25892</t>
+        </is>
+      </c>
+      <c r="H869" s="2" t="n">
+        <v>46293.40177083333</v>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C870" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D870" t="n">
+        <v>39</v>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>25911</t>
+        </is>
+      </c>
+      <c r="H870" s="2" t="n">
+        <v>46293.51270833334</v>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Jacyr Popenda</t>
+        </is>
+      </c>
+      <c r="C871" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D871" t="n">
+        <v>39</v>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>25955</t>
+        </is>
+      </c>
+      <c r="H871" s="2" t="n">
+        <v>46293.68039351852</v>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C872" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D872" t="n">
+        <v>39</v>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>25956</t>
+        </is>
+      </c>
+      <c r="H872" s="2" t="n">
+        <v>46293.68127314815</v>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C873" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D873" t="n">
+        <v>39</v>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>25993</t>
+        </is>
+      </c>
+      <c r="H873" s="2" t="n">
+        <v>46294.41006944444</v>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C874" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D874" t="n">
+        <v>39</v>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>26012</t>
+        </is>
+      </c>
+      <c r="H874" s="2" t="n">
+        <v>46294.5356712963</v>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C875" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D875" t="n">
+        <v>39</v>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>26026</t>
+        </is>
+      </c>
+      <c r="H875" s="2" t="n">
+        <v>46294.644375</v>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C876" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D876" t="n">
+        <v>39</v>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>26102</t>
+        </is>
+      </c>
+      <c r="H876" s="2" t="n">
+        <v>46295.58806712963</v>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K312"/>
+  <dimension ref="A1:K321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16060,16 +16060,16 @@
         <v>2026</v>
       </c>
       <c r="D307" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -16078,11 +16078,11 @@
         </is>
       </c>
       <c r="H307" s="2" t="n">
-        <v>46286.71486111111</v>
+        <v>46289.70833333334</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
@@ -16162,16 +16162,16 @@
         <v>2026</v>
       </c>
       <c r="D309" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -16180,11 +16180,11 @@
         </is>
       </c>
       <c r="H309" s="2" t="n">
-        <v>46287.55743055556</v>
+        <v>46290.43243055556</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -16213,16 +16213,16 @@
         <v>2026</v>
       </c>
       <c r="D310" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -16231,11 +16231,11 @@
         </is>
       </c>
       <c r="H310" s="2" t="n">
-        <v>46293.66871527778</v>
+        <v>46296.66871527778</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
@@ -16264,16 +16264,16 @@
         <v>2026</v>
       </c>
       <c r="D311" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -16282,11 +16282,11 @@
         </is>
       </c>
       <c r="H311" s="2" t="n">
-        <v>46294.3765162037</v>
+        <v>46297.3765162037</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
@@ -16342,10 +16342,469 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D313" t="n">
+        <v>40</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>26409</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="n">
+        <v>46304.62949074074</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr">
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D314" t="n">
+        <v>40</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>26428</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="n">
+        <v>46304.68194444444</v>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D315" t="n">
+        <v>40</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>26484</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="n">
+        <v>46307.48572916666</v>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D316" t="n">
+        <v>40</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>26803</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="n">
+        <v>46307.66666666666</v>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D317" t="n">
+        <v>40</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>26804</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="n">
+        <v>46307.66666666666</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D318" t="n">
+        <v>40</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>26805</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="n">
+        <v>46307.66666666666</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D319" t="n">
+        <v>40</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>26817</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="n">
+        <v>46307.66666666666</v>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D320" t="n">
+        <v>40</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>26818</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="n">
+        <v>46307.66666666666</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>SPN</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Mara Moraes</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D321" t="n">
+        <v>40</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>26819</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="n">
+        <v>46307.66666666666</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -16362,7 +16821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K876"/>
+  <dimension ref="A1:K911"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52188,16 +52647,16 @@
         <v>2026</v>
       </c>
       <c r="D703" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -52206,11 +52665,11 @@
         </is>
       </c>
       <c r="H703" s="2" t="n">
-        <v>46241.55983796297</v>
+        <v>46274.57152777778</v>
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
@@ -59508,7 +59967,7 @@
       </c>
       <c r="J846" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K846" t="inlineStr">
@@ -59559,7 +60018,7 @@
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K847" t="inlineStr">
@@ -60144,16 +60603,16 @@
         <v>2026</v>
       </c>
       <c r="D859" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="G859" t="inlineStr">
@@ -60162,11 +60621,11 @@
         </is>
       </c>
       <c r="H859" s="2" t="n">
-        <v>46287.71019675926</v>
+        <v>46290.70833333334</v>
       </c>
       <c r="I859" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="J859" t="inlineStr">
@@ -60290,36 +60749,36 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Cleovan Profeta</t>
         </is>
       </c>
       <c r="C862" t="n">
         <v>2026</v>
       </c>
       <c r="D862" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="G862" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>25827</t>
         </is>
       </c>
       <c r="H862" s="2" t="n">
-        <v>46286.40253472222</v>
+        <v>46294.64449074074</v>
       </c>
       <c r="I862" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="J862" t="inlineStr">
@@ -60341,7 +60800,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C863" t="n">
@@ -60375,7 +60834,7 @@
       </c>
       <c r="J863" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K863" t="inlineStr">
@@ -60392,7 +60851,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>Michel Pessoa</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C864" t="n">
@@ -60413,11 +60872,11 @@
       </c>
       <c r="G864" t="inlineStr">
         <is>
-          <t>25793</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="H864" s="2" t="n">
-        <v>46290.41263888889</v>
+        <v>46293.37362268518</v>
       </c>
       <c r="I864" t="inlineStr">
         <is>
@@ -60426,7 +60885,7 @@
       </c>
       <c r="J864" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K864" t="inlineStr">
@@ -60443,7 +60902,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Jose Ortiz</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C865" t="n">
@@ -60464,11 +60923,11 @@
       </c>
       <c r="G865" t="inlineStr">
         <is>
-          <t>25818</t>
+          <t>25892</t>
         </is>
       </c>
       <c r="H865" s="2" t="n">
-        <v>46290.62369212963</v>
+        <v>46293.40177083333</v>
       </c>
       <c r="I865" t="inlineStr">
         <is>
@@ -60477,7 +60936,7 @@
       </c>
       <c r="J865" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K865" t="inlineStr">
@@ -60494,7 +60953,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>Cleovan Profeta</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -60515,11 +60974,11 @@
       </c>
       <c r="G866" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>25993</t>
         </is>
       </c>
       <c r="H866" s="2" t="n">
-        <v>46290.64403935185</v>
+        <v>46294.41006944444</v>
       </c>
       <c r="I866" t="inlineStr">
         <is>
@@ -60528,7 +60987,7 @@
       </c>
       <c r="J866" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K866" t="inlineStr">
@@ -60545,7 +61004,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>patrick doyle</t>
+          <t>Erick Silva</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -60566,11 +61025,11 @@
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>25869</t>
+          <t>26026</t>
         </is>
       </c>
       <c r="H867" s="2" t="n">
-        <v>46293.30106481481</v>
+        <v>46294.644375</v>
       </c>
       <c r="I867" t="inlineStr">
         <is>
@@ -60579,7 +61038,7 @@
       </c>
       <c r="J867" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K867" t="inlineStr">
@@ -60617,11 +61076,11 @@
       </c>
       <c r="G868" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>26102</t>
         </is>
       </c>
       <c r="H868" s="2" t="n">
-        <v>46293.37362268518</v>
+        <v>46295.58806712963</v>
       </c>
       <c r="I868" t="inlineStr">
         <is>
@@ -60630,7 +61089,7 @@
       </c>
       <c r="J868" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K868" t="inlineStr">
@@ -60647,7 +61106,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Jacyr Popenda</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -60668,11 +61127,11 @@
       </c>
       <c r="G869" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="H869" s="2" t="n">
-        <v>46293.40177083333</v>
+        <v>46293.68039351852</v>
       </c>
       <c r="I869" t="inlineStr">
         <is>
@@ -60681,7 +61140,7 @@
       </c>
       <c r="J869" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K869" t="inlineStr">
@@ -60698,7 +61157,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Nicolau Berlandi</t>
+          <t>Jose Ortiz</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -60719,11 +61178,11 @@
       </c>
       <c r="G870" t="inlineStr">
         <is>
-          <t>25911</t>
+          <t>25818</t>
         </is>
       </c>
       <c r="H870" s="2" t="n">
-        <v>46293.51270833334</v>
+        <v>46290.62369212963</v>
       </c>
       <c r="I870" t="inlineStr">
         <is>
@@ -60732,7 +61191,7 @@
       </c>
       <c r="J870" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K870" t="inlineStr">
@@ -60749,7 +61208,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Jacyr Popenda</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -60770,11 +61229,11 @@
       </c>
       <c r="G871" t="inlineStr">
         <is>
-          <t>25955</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="H871" s="2" t="n">
-        <v>46293.68039351852</v>
+        <v>46286.40253472222</v>
       </c>
       <c r="I871" t="inlineStr">
         <is>
@@ -60783,7 +61242,7 @@
       </c>
       <c r="J871" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K871" t="inlineStr">
@@ -60834,7 +61293,7 @@
       </c>
       <c r="J872" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K872" t="inlineStr">
@@ -60851,7 +61310,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Lourival Silva</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -60872,11 +61331,11 @@
       </c>
       <c r="G873" t="inlineStr">
         <is>
-          <t>25993</t>
+          <t>26012</t>
         </is>
       </c>
       <c r="H873" s="2" t="n">
-        <v>46294.41006944444</v>
+        <v>46294.5356712963</v>
       </c>
       <c r="I873" t="inlineStr">
         <is>
@@ -60885,7 +61344,7 @@
       </c>
       <c r="J873" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K873" t="inlineStr">
@@ -60902,7 +61361,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>Lourival Silva</t>
+          <t>Michel Pessoa</t>
         </is>
       </c>
       <c r="C874" t="n">
@@ -60923,11 +61382,11 @@
       </c>
       <c r="G874" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="H874" s="2" t="n">
-        <v>46294.5356712963</v>
+        <v>46290.41263888889</v>
       </c>
       <c r="I874" t="inlineStr">
         <is>
@@ -60936,7 +61395,7 @@
       </c>
       <c r="J874" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K874" t="inlineStr">
@@ -60953,7 +61412,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>Nicolau Berlandi</t>
         </is>
       </c>
       <c r="C875" t="n">
@@ -60974,11 +61433,11 @@
       </c>
       <c r="G875" t="inlineStr">
         <is>
-          <t>26026</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="H875" s="2" t="n">
-        <v>46294.644375</v>
+        <v>46293.51270833334</v>
       </c>
       <c r="I875" t="inlineStr">
         <is>
@@ -60987,7 +61446,7 @@
       </c>
       <c r="J875" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K875" t="inlineStr">
@@ -61004,7 +61463,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Erick Silva</t>
+          <t>patrick doyle</t>
         </is>
       </c>
       <c r="C876" t="n">
@@ -61025,11 +61484,11 @@
       </c>
       <c r="G876" t="inlineStr">
         <is>
-          <t>26102</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="H876" s="2" t="n">
-        <v>46295.58806712963</v>
+        <v>46293.30106481481</v>
       </c>
       <c r="I876" t="inlineStr">
         <is>
@@ -61038,10 +61497,1795 @@
       </c>
       <c r="J876" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C877" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D877" t="n">
+        <v>40</v>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>26244</t>
+        </is>
+      </c>
+      <c r="H877" s="2" t="n">
+        <v>46301.6024537037</v>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K876" t="inlineStr">
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C878" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D878" t="n">
+        <v>40</v>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>26327</t>
+        </is>
+      </c>
+      <c r="H878" s="2" t="n">
+        <v>46302.58333333334</v>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C879" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D879" t="n">
+        <v>40</v>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>26332</t>
+        </is>
+      </c>
+      <c r="H879" s="2" t="n">
+        <v>46302.58333333334</v>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C880" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D880" t="n">
+        <v>40</v>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>26338</t>
+        </is>
+      </c>
+      <c r="H880" s="2" t="n">
+        <v>46302.58333333334</v>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C881" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D881" t="n">
+        <v>40</v>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>26447</t>
+        </is>
+      </c>
+      <c r="H881" s="2" t="n">
+        <v>46304.58333333334</v>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C882" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D882" t="n">
+        <v>40</v>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>26448</t>
+        </is>
+      </c>
+      <c r="H882" s="2" t="n">
+        <v>46304.58333333334</v>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C883" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D883" t="n">
+        <v>40</v>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>26449</t>
+        </is>
+      </c>
+      <c r="H883" s="2" t="n">
+        <v>46304.58333333334</v>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C884" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D884" t="n">
+        <v>40</v>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>26450</t>
+        </is>
+      </c>
+      <c r="H884" s="2" t="n">
+        <v>46304.58333333334</v>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C885" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D885" t="n">
+        <v>40</v>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>26477</t>
+        </is>
+      </c>
+      <c r="H885" s="2" t="n">
+        <v>46304.7065162037</v>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C886" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D886" t="n">
+        <v>40</v>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>26478</t>
+        </is>
+      </c>
+      <c r="H886" s="2" t="n">
+        <v>46304.70658564815</v>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C887" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D887" t="n">
+        <v>40</v>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>26519</t>
+        </is>
+      </c>
+      <c r="H887" s="2" t="n">
+        <v>46307.58275462963</v>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C888" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D888" t="n">
+        <v>40</v>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>26533</t>
+        </is>
+      </c>
+      <c r="H888" s="2" t="n">
+        <v>46307.58333333334</v>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C889" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D889" t="n">
+        <v>40</v>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>26534</t>
+        </is>
+      </c>
+      <c r="H889" s="2" t="n">
+        <v>46307.58333333334</v>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C890" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D890" t="n">
+        <v>40</v>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>26535</t>
+        </is>
+      </c>
+      <c r="H890" s="2" t="n">
+        <v>46307.58333333334</v>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C891" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D891" t="n">
+        <v>40</v>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>26536</t>
+        </is>
+      </c>
+      <c r="H891" s="2" t="n">
+        <v>46307.58333333334</v>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C892" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D892" t="n">
+        <v>40</v>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>26557</t>
+        </is>
+      </c>
+      <c r="H892" s="2" t="n">
+        <v>46307.64290509259</v>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C893" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D893" t="n">
+        <v>40</v>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>26572</t>
+        </is>
+      </c>
+      <c r="H893" s="2" t="n">
+        <v>46307.69543981482</v>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D894" t="n">
+        <v>40</v>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>26577</t>
+        </is>
+      </c>
+      <c r="H894" s="2" t="n">
+        <v>46307.70258101852</v>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D895" t="n">
+        <v>40</v>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>26436</t>
+        </is>
+      </c>
+      <c r="H895" s="2" t="n">
+        <v>46302.70833333334</v>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D896" t="n">
+        <v>40</v>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>26170</t>
+        </is>
+      </c>
+      <c r="H896" s="2" t="n">
+        <v>46300.70725694444</v>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D897" t="n">
+        <v>40</v>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>26196</t>
+        </is>
+      </c>
+      <c r="H897" s="2" t="n">
+        <v>46302.62219907407</v>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D898" t="n">
+        <v>40</v>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>26265</t>
+        </is>
+      </c>
+      <c r="H898" s="2" t="n">
+        <v>46301.40614583333</v>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D899" t="n">
+        <v>40</v>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>26480</t>
+        </is>
+      </c>
+      <c r="H899" s="2" t="n">
+        <v>46307.47288194444</v>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D900" t="n">
+        <v>40</v>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>26376</t>
+        </is>
+      </c>
+      <c r="H900" s="2" t="n">
+        <v>46304.4572800926</v>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Jose Ortiz</t>
+        </is>
+      </c>
+      <c r="C901" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D901" t="n">
+        <v>40</v>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>26706</t>
+        </is>
+      </c>
+      <c r="H901" s="2" t="n">
+        <v>46307.70833333334</v>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Kaua Barros</t>
+        </is>
+      </c>
+      <c r="C902" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D902" t="n">
+        <v>40</v>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>26697</t>
+        </is>
+      </c>
+      <c r="H902" s="2" t="n">
+        <v>46307.70833333334</v>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C903" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D903" t="n">
+        <v>40</v>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>26180</t>
+        </is>
+      </c>
+      <c r="H903" s="2" t="n">
+        <v>46304.69444444445</v>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C904" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D904" t="n">
+        <v>40</v>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>26388</t>
+        </is>
+      </c>
+      <c r="H904" s="2" t="n">
+        <v>46307.65486111111</v>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C905" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D905" t="n">
+        <v>40</v>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>26473</t>
+        </is>
+      </c>
+      <c r="H905" s="2" t="n">
+        <v>46304.49122685185</v>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C906" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D906" t="n">
+        <v>40</v>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>26512</t>
+        </is>
+      </c>
+      <c r="H906" s="2" t="n">
+        <v>46307.6875</v>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C907" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D907" t="n">
+        <v>40</v>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>26551</t>
+        </is>
+      </c>
+      <c r="H907" s="2" t="n">
+        <v>46308.37128472222</v>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D908" t="n">
+        <v>40</v>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>25708</t>
+        </is>
+      </c>
+      <c r="H908" s="2" t="n">
+        <v>46293.69662037037</v>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Michel Pessoa</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D909" t="n">
+        <v>40</v>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>26248</t>
+        </is>
+      </c>
+      <c r="H909" s="2" t="n">
+        <v>46302.36896990741</v>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D910" t="n">
+        <v>40</v>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>26146</t>
+        </is>
+      </c>
+      <c r="H910" s="2" t="n">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C911" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D911" t="n">
+        <v>40</v>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>26262</t>
+        </is>
+      </c>
+      <c r="H911" s="2" t="n">
+        <v>46302.40059027778</v>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K911" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -16087,7 +16087,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -16162,16 +16162,16 @@
         <v>2026</v>
       </c>
       <c r="D309" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -16180,11 +16180,11 @@
         </is>
       </c>
       <c r="H309" s="2" t="n">
-        <v>46290.43243055556</v>
+        <v>46287.55743055556</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -16213,16 +16213,16 @@
         <v>2026</v>
       </c>
       <c r="D310" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -16231,11 +16231,11 @@
         </is>
       </c>
       <c r="H310" s="2" t="n">
-        <v>46296.66871527778</v>
+        <v>46293.66871527778</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
@@ -16264,16 +16264,16 @@
         <v>2026</v>
       </c>
       <c r="D311" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -16282,11 +16282,11 @@
         </is>
       </c>
       <c r="H311" s="2" t="n">
-        <v>46297.3765162037</v>
+        <v>46294.3765162037</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
@@ -16366,16 +16366,16 @@
         <v>2026</v>
       </c>
       <c r="D313" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -16384,11 +16384,11 @@
         </is>
       </c>
       <c r="H313" s="2" t="n">
-        <v>46304.62949074074</v>
+        <v>46300.62949074074</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -16699,7 +16699,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -16821,7 +16821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K911"/>
+  <dimension ref="A1:K940"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52674,7 +52674,7 @@
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
@@ -56625,16 +56625,16 @@
         <v>2026</v>
       </c>
       <c r="D781" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
@@ -56643,16 +56643,16 @@
         </is>
       </c>
       <c r="H781" s="2" t="n">
-        <v>46113</v>
+        <v>46127.58086805556</v>
       </c>
       <c r="I781" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J781" t="inlineStr">
         <is>
-          <t>Resolvido</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K781" t="inlineStr">
@@ -60603,16 +60603,16 @@
         <v>2026</v>
       </c>
       <c r="D859" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="G859" t="inlineStr">
@@ -60621,11 +60621,11 @@
         </is>
       </c>
       <c r="H859" s="2" t="n">
-        <v>46290.70833333334</v>
+        <v>46287.71019675926</v>
       </c>
       <c r="I859" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J859" t="inlineStr">
@@ -60756,16 +60756,16 @@
         <v>2026</v>
       </c>
       <c r="D862" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="G862" t="inlineStr">
@@ -60774,11 +60774,11 @@
         </is>
       </c>
       <c r="H862" s="2" t="n">
-        <v>46294.64449074074</v>
+        <v>46290.64403935185</v>
       </c>
       <c r="I862" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J862" t="inlineStr">
@@ -61548,7 +61548,7 @@
       </c>
       <c r="J877" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K877" t="inlineStr">
@@ -61599,7 +61599,7 @@
       </c>
       <c r="J878" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K878" t="inlineStr">
@@ -61650,7 +61650,7 @@
       </c>
       <c r="J879" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K879" t="inlineStr">
@@ -61701,7 +61701,7 @@
       </c>
       <c r="J880" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K880" t="inlineStr">
@@ -61752,7 +61752,7 @@
       </c>
       <c r="J881" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K881" t="inlineStr">
@@ -61803,7 +61803,7 @@
       </c>
       <c r="J882" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K882" t="inlineStr">
@@ -61854,7 +61854,7 @@
       </c>
       <c r="J883" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K883" t="inlineStr">
@@ -61905,7 +61905,7 @@
       </c>
       <c r="J884" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K884" t="inlineStr">
@@ -61956,7 +61956,7 @@
       </c>
       <c r="J885" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K885" t="inlineStr">
@@ -62007,7 +62007,7 @@
       </c>
       <c r="J886" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K886" t="inlineStr">
@@ -62058,7 +62058,7 @@
       </c>
       <c r="J887" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K887" t="inlineStr">
@@ -62109,7 +62109,7 @@
       </c>
       <c r="J888" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K888" t="inlineStr">
@@ -62160,7 +62160,7 @@
       </c>
       <c r="J889" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K889" t="inlineStr">
@@ -62211,7 +62211,7 @@
       </c>
       <c r="J890" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K890" t="inlineStr">
@@ -62262,7 +62262,7 @@
       </c>
       <c r="J891" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K891" t="inlineStr">
@@ -62313,7 +62313,7 @@
       </c>
       <c r="J892" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K892" t="inlineStr">
@@ -62364,7 +62364,7 @@
       </c>
       <c r="J893" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K893" t="inlineStr">
@@ -62415,7 +62415,7 @@
       </c>
       <c r="J894" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K894" t="inlineStr">
@@ -62466,7 +62466,7 @@
       </c>
       <c r="J895" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K895" t="inlineStr">
@@ -62517,7 +62517,7 @@
       </c>
       <c r="J896" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K896" t="inlineStr">
@@ -62568,7 +62568,7 @@
       </c>
       <c r="J897" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K897" t="inlineStr">
@@ -62592,16 +62592,16 @@
         <v>2026</v>
       </c>
       <c r="D898" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="G898" t="inlineStr">
@@ -62610,11 +62610,11 @@
         </is>
       </c>
       <c r="H898" s="2" t="n">
-        <v>46301.40614583333</v>
+        <v>46297.40609953704</v>
       </c>
       <c r="I898" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J898" t="inlineStr">
@@ -62670,7 +62670,7 @@
       </c>
       <c r="J899" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K899" t="inlineStr">
@@ -62721,7 +62721,7 @@
       </c>
       <c r="J900" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K900" t="inlineStr">
@@ -62745,16 +62745,16 @@
         <v>2026</v>
       </c>
       <c r="D901" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="F901" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="G901" t="inlineStr">
@@ -62763,11 +62763,11 @@
         </is>
       </c>
       <c r="H901" s="2" t="n">
-        <v>46307.70833333334</v>
+        <v>46303.7343287037</v>
       </c>
       <c r="I901" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J901" t="inlineStr">
@@ -62823,7 +62823,7 @@
       </c>
       <c r="J902" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K902" t="inlineStr">
@@ -62847,16 +62847,16 @@
         <v>2026</v>
       </c>
       <c r="D903" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="G903" t="inlineStr">
@@ -62865,11 +62865,11 @@
         </is>
       </c>
       <c r="H903" s="2" t="n">
-        <v>46304.69444444445</v>
+        <v>46296.51737268519</v>
       </c>
       <c r="I903" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J903" t="inlineStr">
@@ -62925,7 +62925,7 @@
       </c>
       <c r="J904" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K904" t="inlineStr">
@@ -62949,16 +62949,16 @@
         <v>2026</v>
       </c>
       <c r="D905" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="F905" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="G905" t="inlineStr">
@@ -62967,11 +62967,11 @@
         </is>
       </c>
       <c r="H905" s="2" t="n">
-        <v>46304.49122685185</v>
+        <v>46301.43634259259</v>
       </c>
       <c r="I905" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J905" t="inlineStr">
@@ -63027,7 +63027,7 @@
       </c>
       <c r="J906" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K906" t="inlineStr">
@@ -63078,7 +63078,7 @@
       </c>
       <c r="J907" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K907" t="inlineStr">
@@ -63129,7 +63129,7 @@
       </c>
       <c r="J908" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K908" t="inlineStr">
@@ -63153,16 +63153,16 @@
         <v>2026</v>
       </c>
       <c r="D909" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="F909" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="G909" t="inlineStr">
@@ -63171,11 +63171,11 @@
         </is>
       </c>
       <c r="H909" s="2" t="n">
-        <v>46302.36896990741</v>
+        <v>46297.36896990741</v>
       </c>
       <c r="I909" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J909" t="inlineStr">
@@ -63204,16 +63204,16 @@
         <v>2026</v>
       </c>
       <c r="D910" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="F910" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="G910" t="inlineStr">
@@ -63222,11 +63222,11 @@
         </is>
       </c>
       <c r="H910" s="2" t="n">
-        <v>46300.70833333334</v>
+        <v>46296.3125</v>
       </c>
       <c r="I910" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J910" t="inlineStr">
@@ -63282,10 +63282,1489 @@
       </c>
       <c r="J911" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C912" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D912" t="n">
+        <v>41</v>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>26630</t>
+        </is>
+      </c>
+      <c r="H912" s="2" t="n">
+        <v>46302.69133101852</v>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K911" t="inlineStr">
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C913" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D913" t="n">
+        <v>41</v>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>26909</t>
+        </is>
+      </c>
+      <c r="H913" s="2" t="n">
+        <v>46308.49715277777</v>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C914" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D914" t="n">
+        <v>41</v>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>26938</t>
+        </is>
+      </c>
+      <c r="H914" s="2" t="n">
+        <v>46308.69313657407</v>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C915" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D915" t="n">
+        <v>41</v>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>26950</t>
+        </is>
+      </c>
+      <c r="H915" s="2" t="n">
+        <v>46309.31327546296</v>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C916" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D916" t="n">
+        <v>41</v>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>26995</t>
+        </is>
+      </c>
+      <c r="H916" s="2" t="n">
+        <v>46309.53725694444</v>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C917" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D917" t="n">
+        <v>41</v>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>26912</t>
+        </is>
+      </c>
+      <c r="H917" s="2" t="n">
+        <v>46308.57207175926</v>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C918" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D918" t="n">
+        <v>41</v>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>26953</t>
+        </is>
+      </c>
+      <c r="H918" s="2" t="n">
+        <v>46309.32534722222</v>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J918" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C919" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D919" t="n">
+        <v>41</v>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>26968</t>
+        </is>
+      </c>
+      <c r="H919" s="2" t="n">
+        <v>46309.37296296296</v>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C920" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D920" t="n">
+        <v>41</v>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>27045</t>
+        </is>
+      </c>
+      <c r="H920" s="2" t="n">
+        <v>46310.24324074074</v>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C921" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D921" t="n">
+        <v>41</v>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>26844</t>
+        </is>
+      </c>
+      <c r="H921" s="2" t="n">
+        <v>46307.69796296296</v>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Felipe Nascimento</t>
+        </is>
+      </c>
+      <c r="C922" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D922" t="n">
+        <v>41</v>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>27064</t>
+        </is>
+      </c>
+      <c r="H922" s="2" t="n">
+        <v>46310.36886574074</v>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Guilherme Worel</t>
+        </is>
+      </c>
+      <c r="C923" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D923" t="n">
+        <v>41</v>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>26532</t>
+        </is>
+      </c>
+      <c r="H923" s="2" t="n">
+        <v>46302.19131944444</v>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C924" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D924" t="n">
+        <v>41</v>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>24455</t>
+        </is>
+      </c>
+      <c r="H924" s="2" t="n">
+        <v>46269.5593287037</v>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D925" t="n">
+        <v>41</v>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>26604</t>
+        </is>
+      </c>
+      <c r="H925" s="2" t="n">
+        <v>46302.58886574074</v>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C926" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D926" t="n">
+        <v>41</v>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>26628</t>
+        </is>
+      </c>
+      <c r="H926" s="2" t="n">
+        <v>46302.68869212963</v>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J926" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C927" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D927" t="n">
+        <v>41</v>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>26629</t>
+        </is>
+      </c>
+      <c r="H927" s="2" t="n">
+        <v>46302.69091435185</v>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D928" t="n">
+        <v>41</v>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>26632</t>
+        </is>
+      </c>
+      <c r="H928" s="2" t="n">
+        <v>46302.69332175926</v>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D929" t="n">
+        <v>41</v>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>26680</t>
+        </is>
+      </c>
+      <c r="H929" s="2" t="n">
+        <v>46303.4894212963</v>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D930" t="n">
+        <v>41</v>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>26760</t>
+        </is>
+      </c>
+      <c r="H930" s="2" t="n">
+        <v>46304.60123842592</v>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J930" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D931" t="n">
+        <v>41</v>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>26783</t>
+        </is>
+      </c>
+      <c r="H931" s="2" t="n">
+        <v>46304.67939814815</v>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C932" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D932" t="n">
+        <v>41</v>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>26887</t>
+        </is>
+      </c>
+      <c r="H932" s="2" t="n">
+        <v>46308.40929398148</v>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C933" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D933" t="n">
+        <v>41</v>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>26936</t>
+        </is>
+      </c>
+      <c r="H933" s="2" t="n">
+        <v>46308.679375</v>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C934" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D934" t="n">
+        <v>41</v>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>26940</t>
+        </is>
+      </c>
+      <c r="H934" s="2" t="n">
+        <v>46308.70835648148</v>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C935" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D935" t="n">
+        <v>41</v>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>26945</t>
+        </is>
+      </c>
+      <c r="H935" s="2" t="n">
+        <v>46309.26998842593</v>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C936" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D936" t="n">
+        <v>41</v>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>26997</t>
+        </is>
+      </c>
+      <c r="H936" s="2" t="n">
+        <v>46309.54741898148</v>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C937" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D937" t="n">
+        <v>41</v>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>27000</t>
+        </is>
+      </c>
+      <c r="H937" s="2" t="n">
+        <v>46309.55917824074</v>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C938" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D938" t="n">
+        <v>41</v>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>26569</t>
+        </is>
+      </c>
+      <c r="H938" s="2" t="n">
+        <v>46302.4422337963</v>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Nicolau Berlandi</t>
+        </is>
+      </c>
+      <c r="C939" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D939" t="n">
+        <v>41</v>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>26943</t>
+        </is>
+      </c>
+      <c r="H939" s="2" t="n">
+        <v>46309.21380787037</v>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C940" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D940" t="n">
+        <v>41</v>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>27059</t>
+        </is>
+      </c>
+      <c r="H940" s="2" t="n">
+        <v>46310.35138888889</v>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K940" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K321"/>
+  <dimension ref="A1:K326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16150,7 +16150,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>SPN</t>
+          <t>ITI</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -16162,16 +16162,16 @@
         <v>2026</v>
       </c>
       <c r="D309" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -16201,7 +16201,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SPN</t>
+          <t>ITI</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -16213,16 +16213,16 @@
         <v>2026</v>
       </c>
       <c r="D310" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -16235,7 +16235,7 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
@@ -16252,7 +16252,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>SPN</t>
+          <t>ITI</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -16264,16 +16264,16 @@
         <v>2026</v>
       </c>
       <c r="D311" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
@@ -16354,7 +16354,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>SPN</t>
+          <t>ITI</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -16366,16 +16366,16 @@
         <v>2026</v>
       </c>
       <c r="D313" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -16388,7 +16388,7 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
@@ -16805,6 +16805,261 @@
         </is>
       </c>
       <c r="K321" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Gabriel Coelho</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D322" t="n">
+        <v>42</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>27027</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="n">
+        <v>46309.6562962963</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D323" t="n">
+        <v>42</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>27093</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="n">
+        <v>46310.56311342592</v>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Anderson Giese</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D324" t="n">
+        <v>42</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>27115</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="n">
+        <v>46310.64746527778</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D325" t="n">
+        <v>42</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>27174</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="n">
+        <v>46311.47039351852</v>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Willian Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Higor Jesus</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D326" t="n">
+        <v>42</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>27495</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="n">
+        <v>46316.35155092592</v>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
         <is>
           <t>Willian Rios</t>
         </is>
@@ -16821,7 +17076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K940"/>
+  <dimension ref="A1:K971"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56625,16 +56880,16 @@
         <v>2026</v>
       </c>
       <c r="D781" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
@@ -56647,7 +56902,7 @@
       </c>
       <c r="I781" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="J781" t="inlineStr">
@@ -60603,16 +60858,16 @@
         <v>2026</v>
       </c>
       <c r="D859" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="G859" t="inlineStr">
@@ -60625,7 +60880,7 @@
       </c>
       <c r="I859" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="J859" t="inlineStr">
@@ -60756,16 +61011,16 @@
         <v>2026</v>
       </c>
       <c r="D862" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="G862" t="inlineStr">
@@ -60778,7 +61033,7 @@
       </c>
       <c r="I862" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="J862" t="inlineStr">
@@ -62619,7 +62874,7 @@
       </c>
       <c r="J898" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K898" t="inlineStr">
@@ -62772,7 +63027,7 @@
       </c>
       <c r="J901" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K901" t="inlineStr">
@@ -62847,16 +63102,16 @@
         <v>2026</v>
       </c>
       <c r="D903" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="G903" t="inlineStr">
@@ -62869,7 +63124,7 @@
       </c>
       <c r="I903" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="J903" t="inlineStr">
@@ -62949,16 +63204,16 @@
         <v>2026</v>
       </c>
       <c r="D905" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="F905" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="G905" t="inlineStr">
@@ -62971,7 +63226,7 @@
       </c>
       <c r="I905" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="J905" t="inlineStr">
@@ -63180,7 +63435,7 @@
       </c>
       <c r="J909" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K909" t="inlineStr">
@@ -63231,7 +63486,7 @@
       </c>
       <c r="J910" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K910" t="inlineStr">
@@ -63333,7 +63588,7 @@
       </c>
       <c r="J912" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K912" t="inlineStr">
@@ -63357,16 +63612,16 @@
         <v>2026</v>
       </c>
       <c r="D913" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="F913" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="G913" t="inlineStr">
@@ -63379,7 +63634,7 @@
       </c>
       <c r="I913" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="J913" t="inlineStr">
@@ -63435,7 +63690,7 @@
       </c>
       <c r="J914" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K914" t="inlineStr">
@@ -63486,7 +63741,7 @@
       </c>
       <c r="J915" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K915" t="inlineStr">
@@ -63510,16 +63765,16 @@
         <v>2026</v>
       </c>
       <c r="D916" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="F916" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="G916" t="inlineStr">
@@ -63532,7 +63787,7 @@
       </c>
       <c r="I916" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="J916" t="inlineStr">
@@ -63588,7 +63843,7 @@
       </c>
       <c r="J917" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K917" t="inlineStr">
@@ -63639,7 +63894,7 @@
       </c>
       <c r="J918" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K918" t="inlineStr">
@@ -63690,7 +63945,7 @@
       </c>
       <c r="J919" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K919" t="inlineStr">
@@ -63741,7 +63996,7 @@
       </c>
       <c r="J920" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K920" t="inlineStr">
@@ -63765,16 +64020,16 @@
         <v>2026</v>
       </c>
       <c r="D921" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="F921" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="G921" t="inlineStr">
@@ -63787,7 +64042,7 @@
       </c>
       <c r="I921" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="J921" t="inlineStr">
@@ -63843,7 +64098,7 @@
       </c>
       <c r="J922" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K922" t="inlineStr">
@@ -63894,7 +64149,7 @@
       </c>
       <c r="J923" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K923" t="inlineStr">
@@ -63945,7 +64200,7 @@
       </c>
       <c r="J924" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K924" t="inlineStr">
@@ -63996,7 +64251,7 @@
       </c>
       <c r="J925" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K925" t="inlineStr">
@@ -64047,7 +64302,7 @@
       </c>
       <c r="J926" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K926" t="inlineStr">
@@ -64098,7 +64353,7 @@
       </c>
       <c r="J927" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K927" t="inlineStr">
@@ -64149,7 +64404,7 @@
       </c>
       <c r="J928" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K928" t="inlineStr">
@@ -64200,7 +64455,7 @@
       </c>
       <c r="J929" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K929" t="inlineStr">
@@ -64251,7 +64506,7 @@
       </c>
       <c r="J930" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K930" t="inlineStr">
@@ -64302,7 +64557,7 @@
       </c>
       <c r="J931" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K931" t="inlineStr">
@@ -64353,7 +64608,7 @@
       </c>
       <c r="J932" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K932" t="inlineStr">
@@ -64404,7 +64659,7 @@
       </c>
       <c r="J933" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K933" t="inlineStr">
@@ -64455,7 +64710,7 @@
       </c>
       <c r="J934" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K934" t="inlineStr">
@@ -64506,7 +64761,7 @@
       </c>
       <c r="J935" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K935" t="inlineStr">
@@ -64557,7 +64812,7 @@
       </c>
       <c r="J936" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K936" t="inlineStr">
@@ -64608,7 +64863,7 @@
       </c>
       <c r="J937" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K937" t="inlineStr">
@@ -64659,7 +64914,7 @@
       </c>
       <c r="J938" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K938" t="inlineStr">
@@ -64710,7 +64965,7 @@
       </c>
       <c r="J939" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Resolvido</t>
         </is>
       </c>
       <c r="K939" t="inlineStr">
@@ -64761,10 +65016,1591 @@
       </c>
       <c r="J940" t="inlineStr">
         <is>
+          <t>Resolvido</t>
+        </is>
+      </c>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C941" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D941" t="n">
+        <v>42</v>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>27100</t>
+        </is>
+      </c>
+      <c r="H941" s="2" t="n">
+        <v>46310.59967592593</v>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J941" t="inlineStr">
+        <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K940" t="inlineStr">
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C942" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D942" t="n">
+        <v>42</v>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>27106</t>
+        </is>
+      </c>
+      <c r="H942" s="2" t="n">
+        <v>46310.61927083333</v>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C943" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D943" t="n">
+        <v>42</v>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>27120</t>
+        </is>
+      </c>
+      <c r="H943" s="2" t="n">
+        <v>46310.66613425926</v>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C944" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D944" t="n">
+        <v>42</v>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>27133</t>
+        </is>
+      </c>
+      <c r="H944" s="2" t="n">
+        <v>46311.18515046296</v>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C945" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D945" t="n">
+        <v>42</v>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>27160</t>
+        </is>
+      </c>
+      <c r="H945" s="2" t="n">
+        <v>46311.38689814815</v>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C946" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D946" t="n">
+        <v>42</v>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>27210</t>
+        </is>
+      </c>
+      <c r="H946" s="2" t="n">
+        <v>46311.69034722223</v>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C947" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D947" t="n">
+        <v>42</v>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>27281</t>
+        </is>
+      </c>
+      <c r="H947" s="2" t="n">
+        <v>46314.36944444444</v>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Erick Silva</t>
+        </is>
+      </c>
+      <c r="C948" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D948" t="n">
+        <v>42</v>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>27306</t>
+        </is>
+      </c>
+      <c r="H948" s="2" t="n">
+        <v>46314.45193287037</v>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C949" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D949" t="n">
+        <v>42</v>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>27359</t>
+        </is>
+      </c>
+      <c r="H949" s="2" t="n">
+        <v>46314.64789351852</v>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Edson Junior</t>
+        </is>
+      </c>
+      <c r="C950" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D950" t="n">
+        <v>42</v>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>27367</t>
+        </is>
+      </c>
+      <c r="H950" s="2" t="n">
+        <v>46314.67163194445</v>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C951" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D951" t="n">
+        <v>42</v>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>27385</t>
+        </is>
+      </c>
+      <c r="H951" s="2" t="n">
+        <v>46315.2691087963</v>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C952" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D952" t="n">
+        <v>42</v>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>27397</t>
+        </is>
+      </c>
+      <c r="H952" s="2" t="n">
+        <v>46315.3434375</v>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C953" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D953" t="n">
+        <v>42</v>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>27403</t>
+        </is>
+      </c>
+      <c r="H953" s="2" t="n">
+        <v>46315.35857638889</v>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C954" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D954" t="n">
+        <v>42</v>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>27404</t>
+        </is>
+      </c>
+      <c r="H954" s="2" t="n">
+        <v>46315.35956018518</v>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C955" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D955" t="n">
+        <v>42</v>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>27406</t>
+        </is>
+      </c>
+      <c r="H955" s="2" t="n">
+        <v>46315.37359953704</v>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C956" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D956" t="n">
+        <v>42</v>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>27407</t>
+        </is>
+      </c>
+      <c r="H956" s="2" t="n">
+        <v>46315.38577546296</v>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C957" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D957" t="n">
+        <v>42</v>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>27410</t>
+        </is>
+      </c>
+      <c r="H957" s="2" t="n">
+        <v>46315.4021875</v>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C958" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D958" t="n">
+        <v>42</v>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>27416</t>
+        </is>
+      </c>
+      <c r="H958" s="2" t="n">
+        <v>46315.43866898148</v>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C959" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D959" t="n">
+        <v>42</v>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>27417</t>
+        </is>
+      </c>
+      <c r="H959" s="2" t="n">
+        <v>46315.43900462963</v>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C960" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D960" t="n">
+        <v>42</v>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>27418</t>
+        </is>
+      </c>
+      <c r="H960" s="2" t="n">
+        <v>46315.44021990741</v>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C961" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D961" t="n">
+        <v>42</v>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>27422</t>
+        </is>
+      </c>
+      <c r="H961" s="2" t="n">
+        <v>46315.46162037037</v>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C962" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D962" t="n">
+        <v>42</v>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>27424</t>
+        </is>
+      </c>
+      <c r="H962" s="2" t="n">
+        <v>46315.48903935185</v>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C963" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D963" t="n">
+        <v>42</v>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>27433</t>
+        </is>
+      </c>
+      <c r="H963" s="2" t="n">
+        <v>46315.59074074074</v>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C964" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D964" t="n">
+        <v>42</v>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>27438</t>
+        </is>
+      </c>
+      <c r="H964" s="2" t="n">
+        <v>46315.62258101852</v>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C965" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D965" t="n">
+        <v>42</v>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>27458</t>
+        </is>
+      </c>
+      <c r="H965" s="2" t="n">
+        <v>46315.68769675926</v>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C966" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D966" t="n">
+        <v>42</v>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>27462</t>
+        </is>
+      </c>
+      <c r="H966" s="2" t="n">
+        <v>46315.70314814815</v>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C967" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D967" t="n">
+        <v>42</v>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>27467</t>
+        </is>
+      </c>
+      <c r="H967" s="2" t="n">
+        <v>46315.71918981482</v>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C968" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D968" t="n">
+        <v>42</v>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>27492</t>
+        </is>
+      </c>
+      <c r="H968" s="2" t="n">
+        <v>46316.33706018519</v>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Alana Oliveira</t>
+        </is>
+      </c>
+      <c r="C969" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D969" t="n">
+        <v>42</v>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>27503</t>
+        </is>
+      </c>
+      <c r="H969" s="2" t="n">
+        <v>46316.38402777778</v>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Sostenes Silva</t>
+        </is>
+      </c>
+      <c r="C970" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D970" t="n">
+        <v>42</v>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>27520</t>
+        </is>
+      </c>
+      <c r="H970" s="2" t="n">
+        <v>46316.46012731481</v>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>Emerson Simette</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>ITI</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Lourival Silva</t>
+        </is>
+      </c>
+      <c r="C971" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D971" t="n">
+        <v>42</v>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>27540</t>
+        </is>
+      </c>
+      <c r="H971" s="2" t="n">
+        <v>46316.53737268518</v>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K971" t="inlineStr">
         <is>
           <t>Emerson Simette</t>
         </is>

--- a/data/base/consolidado.xlsx
+++ b/data/base/consolidado.xlsx
@@ -16150,7 +16150,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ITI</t>
+          <t>SPN</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -16201,7 +16201,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ITI</t>
+          <t>SPN</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -16252,7 +16252,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ITI</t>
+          <t>SPN</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -16354,7 +16354,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ITI</t>
+          <t>SPN</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -16813,7 +16813,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ITI</t>
+          <t>SPN</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -16864,7 +16864,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ITI</t>
+          <t>SPN</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -16915,7 +16915,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ITI</t>
+          <t>SPN</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -16966,7 +16966,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ITI</t>
+          <t>SPN</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -17017,7 +17017,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ITI</t>
+          <t>SPN</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
